--- a/daily_matches/job_matches_2026-06-30.xlsx
+++ b/daily_matches/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Forward Deployment Engineer</t>
+          <t>Software Engineer III - Visual AI Technology</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, Glue, Redshift, BigQuery, Synapse, Kinesis, Docker, Kubernetes, CI/CD</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, BigQuery, MLflow, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea91a33e0a092959</t>
+          <t>https://www.indeed.com/viewjob?jk=2bb194dac269cfc4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data and Insight Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, S3, FastAPI, Docker</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, MLflow, CI/CD, Databricks, PySpark, Hadoop, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1996dbb61f895d</t>
+          <t>https://www.indeed.com/viewjob?jk=cece0455bb6da18d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Software Engineer III-ETL/AI</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, S3, Redshift, Data Lake, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2de7adcc27fce6</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb2fa0a1c1af3df</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ML Search Engineer</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,102 +601,102 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3eed5895ede4859</t>
+          <t>https://www.indeed.com/viewjob?jk=6c8650d270076806</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - GCP</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Data Sherpas</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Terraform, Git, BigQuery, Hadoop</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=212dc5034cb8bca8</t>
+          <t>https://www.indeed.com/viewjob?jk=577e95a781bd4589</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Engineer and Architect</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Lake Saint Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, MLflow, CI/CD, Databricks, Redshift</t>
+          <t>RAG, Copilot, S3, EC2, Docker, Kubernetes, CI/CD, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f0ddbe29bf07cc0</t>
+          <t>https://www.indeed.com/viewjob?jk=bc2775012dc3e1f4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Dir, Full Stack Data Scientist</t>
+          <t>Senior Software Engineer, Integrations (Databases) - Hiring Sprint</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bayer</t>
+          <t>Airbyte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>RAG, Prompt Engineering, S3, BigQuery, CI/CD, GitHub Actions, Git, Databricks, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5df2a862bf9db8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0ead42f0db52dd0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist I</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Green Cabbage</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Warrendale, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, Keras, NLTK, CI/CD, Git, NoSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f956bd5a766ffd47</t>
+          <t>https://www.indeed.com/viewjob?jk=5703940eacfe4257</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Kinesis, Docker, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b91053d73a5b33fa</t>
+          <t>https://www.indeed.com/viewjob?jk=3fdf8e05e3832326</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Search Engineer</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Motion</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Docker, Git, PostgreSQL, MySQL, MongoDB</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b805c6c3ef2ef74</t>
+          <t>https://www.indeed.com/viewjob?jk=e28f7c9f9313edca</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Data Lake, Snowflake, Databricks, BigQuery, Redshift, PostgreSQL, Tableau</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75cb5876ca6eeca</t>
+          <t>https://www.indeed.com/viewjob?jk=1655be98963b6d30</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Sales Engineer - DevTools</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Avaya</t>
+          <t>Perforce Software</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, GitHub Actions, Terraform, Git, Databricks, PySpark, Power BI, Matplotlib, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=626f550b7d7b1c09</t>
+          <t>https://www.indeed.com/viewjob?jk=d57dce62ea127658</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java FSD- GenAI</t>
+          <t>AI Native Builder</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, FAISS, Pinecone, Docker, Kubernetes, Python, SQL</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db5b688ad6a99d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=d734e7ef9a655ae9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer (Agency Temp)</t>
+          <t>AI Native Builder</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Cortex, Snowflake, Databricks, PySpark, Tableau, Power BI</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ec69ba27334413b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ebf4addde4aec8c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Native Builder</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Data Lake, FastAPI, Apache Airflow, Snowflake, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f49ef023c8c96de</t>
+          <t>https://www.indeed.com/viewjob?jk=64c15efcfbb29edc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI Software Engineer - Fixed Income Technology</t>
+          <t>Machine Learning Engineer/AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Acentra Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Pinecone, Prompt Engineering, Docker, CI/CD, Git, Snowflake, Python, SQL</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, TensorFlow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb144a9af33a08ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a6edc5fc07cc2269</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer, Jersey City, NJ - Onsite | In-person presence is mandatory</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Copilot, Docker, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL, R, Java</t>
+          <t>RAG, Gemini, Copilot, S3, EC2, Docker, CI/CD, Terraform, Git, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b357357f3cb8f80</t>
+          <t>https://www.indeed.com/viewjob?jk=1fdbca4cb9ae66f3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer - Java and Spring WebFlux</t>
+          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R</t>
+          <t>BigQuery, Dataflow, Docker, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd37326d3fa0289f</t>
+          <t>https://www.indeed.com/viewjob?jk=12e6bda7c4edc743</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer- Big Data &amp; MCP, Data Foundations</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Databricks, Kafka, PostgreSQL, Power BI, Python, SQL</t>
+          <t>BigQuery, Dataflow, Docker, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f5f1d848e75885</t>
+          <t>https://www.indeed.com/viewjob?jk=c603d89b037c27ac</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>ML Ops Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Circadia Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>RAG, S3, EC2, MLflow, Docker, Apache Airflow, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2490431387959f09</t>
+          <t>https://www.indeed.com/viewjob?jk=b91c752a8c427fd0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Artificial Intelligence Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Amphenol</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashua, NH, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, LLaMA, Redshift, Synapse, Snowflake, Databricks, Redshift</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df0b13a3eb9c3062</t>
+          <t>https://www.indeed.com/viewjob?jk=d5e6ac81e0420f06</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Specialist - Software Development &amp; Engineering</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, MongoDB, Python, SQL</t>
+          <t>AI Engineer, RAG, S3, Glue, Athena, Data Lake, CI/CD, Git, Quicksight, Python</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb4a561dc1cddafc</t>
+          <t>https://www.indeed.com/viewjob?jk=92021aa8ff2e1919</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - US</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, CI/CD, GitHub Actions, Terraform, Git, Databricks, NoSQL, Python, SQL</t>
+          <t>AI Engineer, RAG, S3, Glue, Athena, Data Lake, CI/CD, Git, Quicksight, Python</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d0eba562e0eef18</t>
+          <t>https://www.indeed.com/viewjob?jk=74e05275f5681930</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IT360 Inc</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+          <t>AI Engineer, RAG, S3, Glue, Athena, Data Lake, CI/CD, Git, Quicksight, Python</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15d343c668e44bad</t>
+          <t>https://www.indeed.com/viewjob?jk=17c6a7cf5bcefcd6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NLM Cloud Engineer I</t>
+          <t>Data Scientist, Reinforcement Learning</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lexical Intelligence, LLC</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Git, Hadoop, PostgreSQL, MySQL, MongoDB, SQL</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Azure ML, S3, MLflow, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f53c7c2bf6f1f5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f76e08656d77d30d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Innovation Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lewisville, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, TensorFlow, Keras, Kafka, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7cc8319c87c282b</t>
+          <t>https://www.indeed.com/viewjob?jk=67fb9918a3d8eecc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Innovation Software Engineer</t>
+          <t>Data Scientist/Senior Data Scientist</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frontdoor</t>
+          <t>C3 AI</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473234746ee411a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ca43fbc59a01fb3f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - ATI</t>
+          <t>Data Scientist with P&amp;C Insurance Analytics experience</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Robert Half</t>
+          <t>Bourntec Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Glue, CI/CD, Jenkins, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, XGBoost, Databricks, PySpark, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a9b04ee6e058585</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc08726df4587c1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior NoSQL Technical Specialist</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CI/CD, Terraform, MongoDB, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, BigQuery, Snowflake, Databricks, BigQuery, PostgreSQL, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd6b83169c92194</t>
+          <t>https://www.indeed.com/viewjob?jk=ebfe3b1f1e233a71</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Systems &amp; Applications Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Aligned Data Centers</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Terraform, Snowflake, Databricks, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073dcbe12166b408</t>
+          <t>https://www.indeed.com/viewjob?jk=ed0184e76a254e61</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI / Full Stack Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Neiluno Software</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Kubernetes, CI/CD, Terraform, Snowflake, Databricks, Python, R, Java</t>
+          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5283a1c7f91253d8</t>
+          <t>https://www.indeed.com/viewjob?jk=e3d5ec36894636a2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Retrieval &amp; Relevance Engineer (RAG / Hybrid Search)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>iBusiness Funding</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=216e5550ba8c4686</t>
+          <t>https://www.indeed.com/viewjob?jk=a95a70f7d777fc25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Automation Engineer Sales</t>
+          <t>Senior Associate - AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Raya Workforce</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Woodstock, VT, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, CI/CD, Terraform, Git, Snowflake, Python, SQL, R</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, S3, Docker, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21e43ea584d339bf</t>
+          <t>https://www.indeed.com/viewjob?jk=ff296854a0c38d05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Internally Deployed Products</t>
+          <t>Senior Associate - AI Enablement Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ClickUp</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, BigQuery, CI/CD, Terraform, Git, BigQuery, Python, R</t>
+          <t>LangChain, RAG, LLaMA, Hugging Face, S3, Docker, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eb34b68319c8362</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c43b77ad42b08e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - AI/Computer Vision (Camera Systems)</t>
+          <t>Senior Data Scientist - Artificial Intelligence R&amp;D</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, CI/CD, GitHub Actions, Git, Python, R, Optimization</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, MLflow, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7332f557c7a4600</t>
+          <t>https://www.indeed.com/viewjob?jk=503c9bc096b45de5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps Engineer III, AI &amp; Business Automation</t>
+          <t>Machine Learning Intern</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TrueNAS</t>
+          <t>Aivra Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Campbell, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Prompt Engineering, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, FastAPI, Docker, CI/CD, GitHub Actions, Git, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bef6b88eec3d82e</t>
+          <t>https://www.indeed.com/viewjob?jk=2e8a0f3adb10969c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr Engineer - Stores &amp; Supply Chain</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Prompt Engineering, FastAPI, CI/CD, Git, Python, R, A/B Testing</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, Kafka, MongoDB, Cassandra, R, Java, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=764ac26b451d38ac</t>
+          <t>https://www.indeed.com/viewjob?jk=eacf8f14901e715b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>K15 - Embedded Tools &amp; Automation Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dorleco</t>
+          <t>Magnet Forensics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c5e736c74aa8d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e66c582c80db561b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer, Test (Org Modeling)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Prompt Engineering, FastAPI, CI/CD, Git, Python, R, A/B Testing</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70a206f4d3020a8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4df5c37b1c9aa8d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cybersecurity Code Test Engineer</t>
+          <t>Platform Engineer — Cloud Infrastructure (SMTS)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Knightscope, Inc.</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Pinecone, Prompt Engineering, Kubernetes, Terraform, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3272fa35b7b151d8</t>
+          <t>https://www.indeed.com/viewjob?jk=8e20a8e6911c409c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Engineer - Stores &amp; Supply Chain</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Atonom</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Provo, UT, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, Python, SQL, R, Java, Optimization</t>
+          <t>Data Scientist, RAG, Docker, CI/CD, Kafka, MongoDB, Cassandra, R, Java, Scala</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99d9527d99e56dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=834b09654eea1d41</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GreenBox Capital</t>
+          <t>First Service Credit Union</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Databricks, Python, SQL, R, Scala, Optimization, A/B Testing</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, PyTorch, Docker, Python, SQL, R</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b24383111faf1551</t>
+          <t>https://www.indeed.com/viewjob?jk=13f20eadfa9ec212</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Agentic AI Developer</t>
+          <t>Software Engineer III- Python, Databricks</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Calpion/Plutus Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, Python, R, Scala, Optimization</t>
+          <t>RAG, Databricks, Kafka, MongoDB, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b68fed2f10cd3f</t>
+          <t>https://www.indeed.com/viewjob?jk=92f5d55a58f8c38c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Security Engineer</t>
+          <t>Applied AI ML, Senior Associate - Sales Science</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb8c69cfc36a7a6d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb480bca769396c4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevX Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, CI/CD, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9ea8ec8cf6262cf</t>
+          <t>https://www.indeed.com/viewjob?jk=5486719f3bf55b54</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Professional Services Architect (Alteryx Experience Required)</t>
+          <t>Sr. Android Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alteryx</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Gemini, Copilot, CI/CD, GitHub Actions, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=493a0743ec366cb3</t>
+          <t>https://www.indeed.com/viewjob?jk=70433ced582f4f3d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full stack Engineer AI systems</t>
+          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VASERJOB</t>
+          <t>Circana</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RAG, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, PySpark, Hadoop, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed624e563d98659e</t>
+          <t>https://www.indeed.com/viewjob?jk=65c09af802c5ffa3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Full Stack Developer III</t>
+          <t>Senior Engineer, Software Support Engineering (DevOps)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfa3c63c75b9f958</t>
+          <t>https://www.indeed.com/viewjob?jk=c7a4b090c47886ae</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Enterprise Products</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,19 +2176,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0425bbe5cf3dbd</t>
+          <t>https://www.indeed.com/viewjob?jk=19a25e78c3ee22bc</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Big Data Engineers*| HQ: Chicago, IL</t>
+          <t>Senior Application Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Circana</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RAG, PySpark, Hadoop, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Git, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c44ee92aa2c8400</t>
+          <t>https://www.indeed.com/viewjob?jk=04b00b0deb40dfcf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Solutions Architect II - Omnichannel</t>
+          <t>Senior Finance Systems Engineer: Oracle Fusion - Remote, US</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Git, Snowflake, Databricks, Kafka, R, Scala</t>
+          <t>RAG, Copilot, Data Lake, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51e91e41bcce9db6</t>
+          <t>https://www.indeed.com/viewjob?jk=04e3863dd7be7bbc</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III (DevOps)</t>
+          <t>Microsoft Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Babel</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lowell, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>AI Engineer, Data Lake, Git, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b4d3a66db6c7d8d</t>
+          <t>https://www.indeed.com/viewjob?jk=34a4de8e87940939</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Azure Data &amp; AI Architect - Remote US</t>
+          <t>QA Test Automation Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>eGroup Enabling Technologies</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Synapse, CI/CD, Databricks, Power BI, Python, R, Scala</t>
+          <t>Data Scientist, RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b47a8a4a7fcc4c89</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ef306d256ad414</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data &amp; Infrastructure Engineer</t>
+          <t>Sr. Application Software Engineer, Data Analytics</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>workbay</t>
+          <t>SpaceX</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Bastrop, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+          <t>PyTorch, OpenCV, PostgreSQL, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c1c3860689ee6c2</t>
+          <t>https://www.indeed.com/viewjob?jk=79a45e6d5559d680</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NextEra Energy</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Git, Redshift, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, RAG, TensorFlow, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52ef58946951746</t>
+          <t>https://www.indeed.com/viewjob?jk=548cb207ce9820d6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Estero, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, CI/CD, Git, Databricks, Kafka, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,42 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b537ec115b25d9</t>
+          <t>https://www.indeed.com/viewjob?jk=049e21cbadb5f01b</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ee705576083bb1b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-30.xlsx
+++ b/daily_matches/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Willdan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Git, BigQuery</t>
+          <t>Generative AI, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dae99e1ea457637a</t>
+          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior IT Big Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Edgewater Federal Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Cortex, S3, Glue, Kinesis, CI/CD, Git, Snowflake, Databricks, PySpark</t>
+          <t>RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9fc4b01a8878948</t>
+          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Entiovi Technologies Private Limited</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Bengal, IN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Cortex, S3, Glue, Kinesis, CI/CD, Git, Snowflake, Databricks, PySpark</t>
+          <t>AI Engineer, RAG, Prompt Engineering, S3, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de1fca8ed87b85de</t>
+          <t>https://www.indeed.com/viewjob?jk=f89dc1b57a628321</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>Senior Platform Engineer, Data &amp; AI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Polars, Python, SQL</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Terraform, Snowflake, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de33f3f460768669</t>
+          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, Data (L1)</t>
+          <t>Senior AI/.NET Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>MILBANK LLP</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, Databricks, BigQuery, Polars, Python, SQL</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a58fca26aa0b565</t>
+          <t>https://www.indeed.com/viewjob?jk=2c9f5a7b57bd8967</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Union City, NJ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, Python</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kafka, Cassandra, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d63ab0e4452de4</t>
+          <t>https://www.indeed.com/viewjob?jk=288674c91c1a2d02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, S3, CI/CD, Jenkins, Git, PostgreSQL, NoSQL, SQL</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kafka, Cassandra, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=badd3067a5cffe65</t>
+          <t>https://www.indeed.com/viewjob?jk=879679de54fc925e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Agent Engineer Job</t>
+          <t>Embedded Tools &amp; Automation Engineer (Python, CI/CD, Linux, Docker)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Planera</t>
+          <t>KPIT Technologies</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, S3, Docker, CI/CD, Terraform, Git, MongoDB</t>
+          <t>RAG, Docker, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=804f3776d5f68767</t>
+          <t>https://www.indeed.com/viewjob?jk=584da6746d6d0833</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Software Engineer, Enterprise Products</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,252 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302d0aef0da08d5b</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Engineer III- Python, Databricks</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Databricks, Kafka, MongoDB, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af72bf959cb85028</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Applications Engineer 2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Snowflake, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3bebf72dd18ba02e</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c26072112fe74f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63c1e33f47e33923</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30c49ff5a704fb3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Data Analytics and Research Analyst</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Serco</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ff9d242b38a44972</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Performance Marketing Data Analyst</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Crate and Barrel</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Git, Tableau, Power BI, Python, SQL, R, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=094cb54cd4792f0d</t>
+          <t>https://www.indeed.com/viewjob?jk=c61c3648cee5df44</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-30.xlsx
+++ b/daily_matches/job_matches_2026-06-30.xlsx
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI Solutions Engineer Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Willdan</t>
+          <t>Inter-American Development Bank</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Generative AI, Gemini, Copilot, FastAPI, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020391c43706e33</t>
+          <t>https://www.indeed.com/viewjob?jk=c6998cc9fcbd09ee</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior IT Big Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Edgewater Federal Solutions</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=805d9159d3aff63f</t>
+          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Senior Product Software Engineer - Frontend</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Entiovi Technologies Private Limited</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bengal, IN, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, S3, CI/CD, Terraform, Git, PostgreSQL, NoSQL, SQL</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, CI/CD, GitHub Actions, Git, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,137 +566,137 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f89dc1b57a628321</t>
+          <t>https://www.indeed.com/viewjob?jk=46b6918d8d7d456e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer, Data &amp; AI</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>TEAM</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, Terraform, Snowflake, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, CI/CD, Git, Snowflake, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70e3e5b69eb2b62</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd3be45639f7d16</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI/.NET Engineer</t>
+          <t>DevOps and Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MILBANK LLP</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9f5a7b57bd8967</t>
+          <t>https://www.indeed.com/viewjob?jk=165b6d97ce692d63</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Pre-Sales Solutions Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kafka, Cassandra, Python, R, Java, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=288674c91c1a2d02</t>
+          <t>https://www.indeed.com/viewjob?jk=9ab7e0628c4be3c8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Technical Solutioning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kafka, Cassandra, Python, R, Java, Scala</t>
+          <t>Generative AI, RAG, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=879679de54fc925e</t>
+          <t>https://www.indeed.com/viewjob?jk=8edf72a00787a67c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Embedded Tools &amp; Automation Engineer (Python, CI/CD, Linux, Docker)</t>
+          <t>Technical Solutioning Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KPIT Technologies</t>
+          <t>AIG</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=584da6746d6d0833</t>
+          <t>https://www.indeed.com/viewjob?jk=4c3dbaf8f822c14a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Enterprise Products</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GitHub</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, Kinesis, FastAPI, CI/CD, Snowflake, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c61c3648cee5df44</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7cfabb237ea873</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-30.xlsx
+++ b/daily_matches/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Solutions Engineer Consultant</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Inter-American Development Bank</t>
+          <t>6sense</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, Gemini, Copilot, FastAPI, Docker, CI/CD, Git, PostgreSQL, MongoDB, Python</t>
+          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6998cc9fcbd09ee</t>
+          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior ML Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Copilot, MLflow, FastAPI, CI/CD, Terraform, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cfca332d489410</t>
+          <t>https://www.indeed.com/viewjob?jk=5d47490d1b7f4615</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Product Software Engineer - Frontend</t>
+          <t>Senior ML Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, LLaMA, Copilot, CI/CD, GitHub Actions, Git, Python, R</t>
+          <t>Data Scientist, RAG, Copilot, MLflow, FastAPI, CI/CD, Terraform, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46b6918d8d7d456e</t>
+          <t>https://www.indeed.com/viewjob?jk=302fe1f2beb7b4f3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>Global KTech</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd3be45639f7d16</t>
+          <t>https://www.indeed.com/viewjob?jk=34a46650dcb38440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps and Site Reliability Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>HELIX</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Mexico, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Gemini, Copilot, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=165b6d97ce692d63</t>
+          <t>https://www.indeed.com/viewjob?jk=14c3924629b18b1c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pre-Sales Solutions Engineer</t>
+          <t>Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Synapse, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ab7e0628c4be3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Technical Solutioning Engineer</t>
+          <t>AI Engineer - Clinical Communication &amp; Workflow Systems</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>AMETEK</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Mount Prospect, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8edf72a00787a67c</t>
+          <t>https://www.indeed.com/viewjob?jk=48fafb29384f385b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Technical Solutioning Engineer</t>
+          <t>Senior Quality Assurance Engineer (9326321)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AIG</t>
+          <t>Cargomatic</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c3dbaf8f822c14a</t>
+          <t>https://www.indeed.com/viewjob?jk=65a5ea88aecca2a9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Kinesis, FastAPI, CI/CD, Snowflake, Kafka, Python, SQL, R</t>
+          <t>RAG, Kubernetes, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,112 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7cfabb237ea873</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba1fbba3b6536d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Performance Engineer (Analyst)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ralph Lauren</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nutley, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=66f184fff2501aba</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Fabric Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa96eb2e2cadf4c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Fabric Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>EXL Service</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f0400aa605d4f68</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-30.xlsx
+++ b/daily_matches/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer - Temporary Worker</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6sense</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL</t>
+          <t>RAG, Copilot, Redshift, BigQuery, Synapse, Apache Airflow, CI/CD, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05703cc8519b448f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3608ce8fafa5b9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior ML Software Engineer</t>
+          <t>Gen AI Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>QualityAI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, MLflow, FastAPI, CI/CD, Terraform, Git, Databricks, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Hugging Face, Pinecone, Prompt Engineering, GCP Vertex AI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d47490d1b7f4615</t>
+          <t>https://www.indeed.com/viewjob?jk=dd6f26d72223ee99</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior ML Software Engineer</t>
+          <t>Senior Full-Stack Software Engineer – Back-End Focused</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>STAND TOGETHER</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, MLflow, FastAPI, CI/CD, Terraform, Git, Databricks, Python</t>
+          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=302fe1f2beb7b4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=27c394a83edfce01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Full Stack Software Engineer - CostCheck</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Global KTech</t>
+          <t>BlueSight</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
+          <t>RAG, Copilot, S3, Athena, FastAPI, CI/CD, Terraform, PostgreSQL, MySQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34a46650dcb38440</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b724f0ef5f1675</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HELIX</t>
+          <t>EssilorLuxottica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mexico, MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Synapse, Docker, Kubernetes, Git, Databricks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c3924629b18b1c</t>
+          <t>https://www.indeed.com/viewjob?jk=8eb6bda4ac3bf0ba</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II (US)</t>
+          <t>Deep Learning Product Research Engineer - Product Innovation</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2048b8f9fc33e871</t>
+          <t>https://www.indeed.com/viewjob?jk=b10b66cedf0275a3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer - Clinical Communication &amp; Workflow Systems</t>
+          <t>Full Stack Materials Database Programmer for ML/AI Integration</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMETEK</t>
+          <t>Argonne National Laboratory</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mount Prospect, IL, US USA</t>
+          <t>Lemont, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fafb29384f385b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c417989bfd43e7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Quality Assurance Engineer (9326321)</t>
+          <t>Senior AI Engineer 2026 - US</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cargomatic</t>
+          <t>Aimpoint Digital</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Copilot, FastAPI, Kubernetes, CI/CD, Git, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65a5ea88aecca2a9</t>
+          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer - System Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>Bay Systems Consulting, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba1fbba3b6536d5</t>
+          <t>https://www.indeed.com/viewjob?jk=35a55ea23b7b4bb6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Performance Engineer (Analyst)</t>
+          <t>Deep Learning Product Research Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ralph Lauren</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nutley, NJ, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f184fff2501aba</t>
+          <t>https://www.indeed.com/viewjob?jk=82e3272f67d8364d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fabric Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>FANATICS COLLECTIBLES</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,42 +846,427 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa96eb2e2cadf4c9</t>
+          <t>https://www.indeed.com/viewjob?jk=8147e3e6ba6af5e0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fabric Analytics Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>FANATICS COLLECTIBLES</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d35d56bbb4c469b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MediaRadar</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D14" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ABC Legal Services</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Copilot, TensorFlow, PyTorch, AWS SageMaker, Glue, Redshift, Redshift, Python</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44e35851e8a4c900</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Mobile Software Engineer Hybrid</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, Git, BigQuery, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87c312b6a8ac3773</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr. Engineer Cloud</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Safeway</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e6045e715260edf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sr. Engineer Cloud</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Safeway</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, GitHub Actions, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a23596ee64b5afc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KNOTCH, INC.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc2a9cbd0edf34f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Datastores</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Terraform, Kafka, MySQL, Cassandra, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ba7aec323b47559</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sr. Analyst, Data Science</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LPL Financial</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fb6ea5e8732e52f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Platform Security Engineer Hybrid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, Synapse, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0400aa605d4f68</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b2074e7cfcb7261</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer - Unity (Remote)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lingraphica</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21b38121719dc7e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer (Job ID 3021039)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Blue Bell, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b706891a71cca481</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-30.xlsx
+++ b/daily_matches/job_matches_2026-06-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,12 +473,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>Dentsu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3608ce8fafa5b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f79b9ae386c30e15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gen AI Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>QualityAI</t>
+          <t>NiCE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sandy, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, Hugging Face, Pinecone, Prompt Engineering, GCP Vertex AI</t>
+          <t>RAG, Prompt Engineering, Data Lake, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd6f26d72223ee99</t>
+          <t>https://www.indeed.com/viewjob?jk=b189c9b3212dd317</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer – Back-End Focused</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>STAND TOGETHER</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, MongoDB, NoSQL, Python</t>
+          <t>AI Engineer, Machine Learning Engineer, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27c394a83edfce01</t>
+          <t>https://www.indeed.com/viewjob?jk=3da305fd1d9c2c5c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer - CostCheck</t>
+          <t>Data Engineer - Senior Consultant level</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BlueSight</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Athena, FastAPI, CI/CD, Terraform, PostgreSQL, MySQL, Python</t>
+          <t>Data Scientist, RAG, Copilot, Kubernetes, CI/CD, Kafka, Hadoop, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b724f0ef5f1675</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7e8c2fc1da6d00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Architect (P4642)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EssilorLuxottica</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Synapse, Docker, Kubernetes, Git, Databricks</t>
+          <t>Data Scientist, RAG, Cortex, Data Lake, MLflow, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eb6bda4ac3bf0ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1660a4cf0a8045d0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Deep Learning Product Research Engineer - Product Innovation</t>
+          <t>Data Architect (P4642)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>84.51°</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python</t>
+          <t>Data Scientist, RAG, Cortex, Data Lake, MLflow, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b10b66cedf0275a3</t>
+          <t>https://www.indeed.com/viewjob?jk=39b5a4b6b25e561f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Materials Database Programmer for ML/AI Integration</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Argonne National Laboratory</t>
+          <t>Fidelity Investments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lemont, IL, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Kubernetes, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>S3, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c417989bfd43e7</t>
+          <t>https://www.indeed.com/viewjob?jk=675596684c392e8e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer 2026 - US</t>
+          <t>AI &amp; Data Scientist (Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Aimpoint Digital</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Copilot, FastAPI, Kubernetes, CI/CD, Git, Snowflake, Databricks, Python, R</t>
+          <t>Data Scientist, MLflow, Docker, CI/CD, Git, Databricks, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13884b1c57640398</t>
+          <t>https://www.indeed.com/viewjob?jk=c7384adb01a71a5a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Platform Engineer - System Infrastructure Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bay Systems Consulting, Inc.</t>
+          <t>ABC Legal Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Copilot, TensorFlow, PyTorch, AWS SageMaker, Glue, Redshift, Redshift, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a55ea23b7b4bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=cee9c6c11b6de046</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Deep Learning Product Research Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>ABC Legal Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Copilot, TensorFlow, PyTorch, AWS SageMaker, Glue, Redshift, Redshift, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e3272f67d8364d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b6409e07dc66d0d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Software Engineer - AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FANATICS COLLECTIBLES</t>
+          <t>LogicMonitor</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
+          <t>RAG, Data Lake, FastAPI, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8147e3e6ba6af5e0</t>
+          <t>https://www.indeed.com/viewjob?jk=951fb41e37160d69</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Agentic AI/AI Engineer - Generative AI &amp; Machine Learning</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FANATICS COLLECTIBLES</t>
+          <t>Hudson Manpower</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Python, SQL, R</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, BigQuery, BigQuery, MySQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35d56bbb4c469b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a5aeb2b4e9bf8e13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MediaRadar</t>
+          <t>Expedia Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Databricks, Kafka, Python, SQL</t>
+          <t>RAG, S3, Glue, Databricks, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=180b2fb1ba9c363d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4db27c4a07cdc78</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ABC Legal Services</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Copilot, TensorFlow, PyTorch, AWS SageMaker, Glue, Redshift, Redshift, Python</t>
+          <t>RAG, Data Lake, Git, NoSQL, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e35851e8a4c900</t>
+          <t>https://www.indeed.com/viewjob?jk=9850c3aac9cd378a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mobile Software Engineer Hybrid</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Vantor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, BigQuery, Git, BigQuery, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, PostgreSQL, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87c312b6a8ac3773</t>
+          <t>https://www.indeed.com/viewjob?jk=5f96ee89dabd5860</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Engineer Cloud</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Safeway</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, MLflow, Docker, Kubernetes, Terraform, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6045e715260edf</t>
+          <t>https://www.indeed.com/viewjob?jk=cbf9ee70905a9488</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Engineer Cloud</t>
+          <t>Software Engineer - Sr. Consultant level-1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Safeway</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, GitHub Actions, Terraform, Git, Python, R, Java</t>
+          <t>Generative AI, Copilot, Jenkins, Git, Kafka, MySQL, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a23596ee64b5afc6</t>
+          <t>https://www.indeed.com/viewjob?jk=571fcfefda1a27fe</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DevOps Engineer (GCP)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>KNOTCH, INC.</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, R, Scala</t>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc2a9cbd0edf34f9</t>
+          <t>https://www.indeed.com/viewjob?jk=3be165f3f95585e1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II, Datastores</t>
+          <t>Senior Agentic AI Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Terraform, Kafka, MySQL, Cassandra, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, Copilot, Synapse, Snowflake, Databricks, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba7aec323b47559</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9c1c0c16c7dfd7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data Science</t>
+          <t>Senior Agentic AI Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
+          <t>AI Engineer, Generative AI, Copilot, Synapse, Snowflake, Databricks, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,112 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fb6ea5e8732e52f</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AI Platform Security Engineer Hybrid</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Kubernetes, CI/CD, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2074e7cfcb7261</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Software Engineer - Unity (Remote)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Lingraphica</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Princeton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21b38121719dc7e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer (Job ID 3021039)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Blue Bell, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b706891a71cca481</t>
+          <t>https://www.indeed.com/viewjob?jk=1d9daec8971db291</t>
         </is>
       </c>
     </row>
